--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>111621</v>
+        <v>111622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135848884</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135848748</v>
       </c>
       <c r="B7" t="n">
-        <v>99362</v>
+        <v>99363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135848711</v>
       </c>
       <c r="B8" t="n">
-        <v>102778</v>
+        <v>102779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/Grytholmens naturreservat artfynd.xlsx
+++ b/artfynd/Grytholmens naturreservat artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135848412</v>
       </c>
       <c r="B2" t="n">
-        <v>111622</v>
+        <v>111635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>135848884</v>
       </c>
       <c r="B5" t="n">
-        <v>99307</v>
+        <v>99320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>135848748</v>
       </c>
       <c r="B7" t="n">
-        <v>99363</v>
+        <v>99376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         <v>135848711</v>
       </c>
       <c r="B8" t="n">
-        <v>102779</v>
+        <v>102792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
